--- a/assets/r04/sheets/範例玩家角色卡.xlsx
+++ b/assets/r04/sheets/範例玩家角色卡.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="範例玩家角色卡（主管）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="艾琳" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="馬可" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="凜" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="格魯" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,18 +29,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="002B5797"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -49,16 +61,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B5797"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -67,73 +81,73 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
+      <left/>
       <right/>
-      <top/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top/>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -500,206 +514,3242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>範例玩家角色卡（主管）</t>
-        </is>
-      </c>
-    </row>
+          <t>【艾琳】疾風 — 凍結廢土TRPG 時間掠奪者角色卡</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="13" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>欄位</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>內容</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>角色名稱</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>（範例）林主管</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>艾琳</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>疾風</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>玩家名稱</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>玩家A</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>尋人者</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>28 / 護士</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>職位（主管/部長）</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>臨時部長</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>魅力 (Charm)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>湖心城</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>短黑髮，總是綁著馬尾。右手腕有一道凍傷疤痕。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>智力 (Int)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>五大屬性</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>體力 (Phys)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>修正值(ATT-5)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>說明</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>咒力 (Curs)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>移動力/反應</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>心力 (Ment)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>觀察/預判</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>算力上限 (Sanli)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>冷靜/意志力</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>滿意度 (ManYi)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>裝置操作</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>資金 (Zijin)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>經驗/備註</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>擅長調度與外交，初掌部門</t>
-        </is>
-      </c>
-    </row>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>交涉（NEG）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>說服/談判</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>角色圖</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>【在此貼上角色圖片】</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="n"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>移動力（MV）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>格/回合</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="n"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>前兆感知（FS）</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="n"/>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>恐慌閾值（PT）</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="n"/>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>時間抗性（TR）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="8" t="n"/>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>生命值（HP）(最大)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>決心點 RP(最大)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>當前生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>(手動)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>當前決心點</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>靈感點</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>恐慌值</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>起始=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>動機</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>動機類型</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>尋人者</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>動機能力</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>絕不放棄：尋找目標相關知覺檢定時，花1決心點獲優勢</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="13" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>凍結區經驗</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>經驗類型</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>痙攣型賭徒</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>經驗優勢</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>解凍瞬間膽量檢定 難度（DC）-2</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>經驗直覺(被動)</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>恐慌壓力每次解凍只增加一半</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="13" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>創傷</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>創傷類型</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>失去隊友  [未克服]</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>創傷效應(劣勢)</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>隊友處於危險中時，膽量檢定劣勢</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>決心效應(優勢)</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>成功保護隊友時，回復1決心點</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="13" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>還在找的人</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>妹妹艾瑪</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>血親</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>最後位置</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>第三中學（痙攣型凍結區）</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="13" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>基礎防護服 (+1, 時間抗性+1)</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>武器1</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>小刀 (1d4+1, 近戰)</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>武器2</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>(無)</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>探測器</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>初階 (30格/60%)</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>防水文件夾(妹妹照片+地圖), 信號彈x2</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="13" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>應急口糧(天份)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>急救包</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>信號彈</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>粉筆</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>資源</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>廢鐵幣</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>時間結晶(儲存)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>當前負重</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>/15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B16:B21"/>
+  <mergeCells count="36">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A34:B34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【馬可】算盤 — 凍結廢土TRPG 時間掠奪者角色卡</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="13" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>馬可</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>算盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>淘晶者</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>35 / 前倉庫管理員</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>鋼橋鎮</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>略胖，戴著破舊眼鏡。總是穿著太多層衣服——他說「凍怕了」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>五大屬性</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>修正值(ATT-5)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>移動力/反應</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>觀察/預判</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>冷靜/意志力</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>裝置操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>交涉（NEG）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>說服/談判</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>移動力（MV）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>格/回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>前兆感知（FS）</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>恐慌閾值（PT）</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>時間抗性（TR）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>生命值（HP）(最大)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>決心點 RP(最大)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>當前生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>(手動)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>當前決心點</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>靈感點</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>恐慌值</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>起始=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>動機</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>動機類型</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>淘晶者</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>動機能力</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>嗅覺靈敏：評估時間結晶價值自動成功</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="13" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>凍結區經驗</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>經驗類型</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>脈搏型舞者</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>經驗優勢</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>預判下一次解凍準確回合數（技術難度（DC）10）</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>經驗直覺(被動)</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>規律性解凍環境中移動力+1</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="13" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>創傷</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>創傷類型</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>背叛  [未克服]</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>創傷效應(劣勢)</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>與陌生人交涉時劣勢</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>決心效應(優勢)</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>察覺欺騙或埋伏時自動成功</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="13" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>還在找的人</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>合夥人（出賣他的人）</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>虧欠的人</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>最後位置</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>凍結中的工業區倉庫</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="13" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>基礎防護服 (+1, 時間抗性+1)</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>武器1</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>撬棍 (1d6+1, 近戰)</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>武器2</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>(無)</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>探測器</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>改裝探測器 (30格/70%)</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>小保險箱, 黑市聯絡人名單</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="13" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>應急口糧(天份)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>急救包</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>信號彈</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>粉筆</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>資源</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>廢鐵幣</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>時間結晶(儲存)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>當前負重</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>/15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A34:B34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【凜】觀測者 — 凍結廢土TRPG 時間掠奪者角色卡</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="13" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>凜</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>觀測者</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>探索者</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>24 / 前研究生</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>三塔</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>纖瘦，眼神總是望向遠方。口袋裡永遠裝著一本筆記本。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>五大屬性</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>修正值(ATT-5)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>移動力/反應</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>觀察/預判</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>冷靜/意志力</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>裝置操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>交涉（NEG）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>說服/談判</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>移動力（MV）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>格/回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>前兆感知（FS）</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>恐慌閾值（PT）</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>時間抗性（TR）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>生命值（HP）(最大)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>決心點 RP(最大)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>當前生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>(手動)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>當前決心點</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>靈感點</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>恐慌值</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>起始=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>動機</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>動機類型</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>探索者</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>動機能力</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>學者之眼：進入新凍結區時，GM告知一種獨特特徵</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="13" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>凍結區經驗</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>經驗類型</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>呼吸型潛行者</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>經驗優勢</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>感知當前「吸」或「呼」階段（無需擲骰）</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>經驗直覺(被動)</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>呼吸型漸進階段中移動速度不減半</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="13" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>創傷</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>創傷類型</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>時間中毒  [未克服]</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>創傷效應(劣勢)</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>需要精確時機的行動中速度檢定劣勢</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>決心效應(優勢)</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>花1決心點重擲知覺檢定</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="13" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>還在找的人</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>恩師（凍結在某實驗室）</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>導師</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>最後位置</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>凍結前物理研究所</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="13" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>基礎防護服 (+1, 時間抗性+1)</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>武器1</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>徒手 (1d4)</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>武器2</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>(無)</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>探測器</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>初階 (30格/60%)</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>研究筆記, 分析工具包</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="13" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>應急口糧(天份)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>急救包</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>信號彈</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>粉筆</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>資源</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>廢鐵幣</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>時間結晶(儲存)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>當前負重</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>/15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A34:B34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【格魯】硬骨頭 — 凍結廢土TRPG 時間掠奪者角色卡</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="13" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n"/>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>格魯</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>硬骨頭</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>贖罪者</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>42 / 前消防員</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>湖心城</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>魁梧，話少。右手臂有一片部分凍結的皮膚——永遠是冰涼的灰藍色。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>五大屬性</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>修正值(ATT-5)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>移動力/反應</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>觀察/預判</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>冷靜/意志力</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>裝置操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>交涉（NEG）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>說服/談判</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>移動力（MV）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>格/回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>前兆感知（FS）</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>恐慌閾值（PT）</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>時間抗性（TR）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>生命值（HP）(最大)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>決心點 RP(最大)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>當前生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>(手動)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>當前決心點</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>靈感點</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>恐慌值</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>起始=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>動機</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>動機類型</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>贖罪者</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>動機能力</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>不再逃避：創傷類似情境時，花1決心點將劣勢變正常</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="13" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>凍結區經驗</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>經驗類型</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>連鎖型協調者</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>經驗優勢</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>花一個行動警告隊友下一區即將解凍</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>經驗直覺(被動)</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>隊友在視線範圍內膽量檢定+1</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="13" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>創傷</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>創傷類型</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>失去隊友  [未克服]</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>創傷效應(劣勢)</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>隊友處於危險中時，膽量檢定劣勢</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="13" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>決心效應(優勢)</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>成功保護隊友時，回復1決心點</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="13" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>還在找的人</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>被困火場的女孩</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>沒救到的人</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>最後位置</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>凍結中的公寓大樓</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="13" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="12" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>強化防護服 (+2, 時間抗性+1)</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
+      <c r="E48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>武器1</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>消防斧 (1d8, 近戰)</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>武器2</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>(無)</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="13" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>探測器</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>初階 (30格/60%)</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="12" t="n"/>
+      <c r="E51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>道具</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>急救包x1, 遺物(舊消防徽章)</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="13" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>應急口糧(天份)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>急救包</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>信號彈</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>粉筆</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>資源</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>廢鐵幣</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>時間結晶(儲存)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>當前負重</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>專長</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="12" t="n"/>
+      <c r="D63" s="12" t="n"/>
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="13" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>鐵膽 (膽量（GUT）&gt;=7: 恐慌閾值+3)</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="13" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
